--- a/策划/数值文档/class_c.xlsx
+++ b/策划/数值文档/class_c.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>id</t>
   </si>
@@ -61,6 +61,15 @@
     <t>stam_per_vit</t>
   </si>
   <si>
+    <t>hp_add</t>
+  </si>
+  <si>
+    <t>base_stamina</t>
+  </si>
+  <si>
+    <t>block_factor</t>
+  </si>
+  <si>
     <t>to_hit_factor</t>
   </si>
   <si>
@@ -128,6 +137,15 @@
   </si>
   <si>
     <t>每点体力=耐力（官方 StaminaPerVitality，已 ÷4）</t>
+  </si>
+  <si>
+    <t>起始生命加成（官方 charstats.hpadd；与起始体力相加 = 1 级生命）</t>
+  </si>
+  <si>
+    <t>起始耐力上限（官方 charstats.stamina）</t>
+  </si>
+  <si>
+    <t>职业格挡系数（官方 charstats.BlockFactor）</t>
   </si>
   <si>
     <t>命中修正（官方 ToHitFactor）</t>
@@ -557,182 +575,218 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="T2" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="S3" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="T3" t="s">
+        <v>25</v>
+      </c>
+      <c r="U3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="S4" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="T4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" t="s">
+        <v>46</v>
+      </c>
+      <c r="V4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -740,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E5">
         <v>20</v>
@@ -782,16 +836,25 @@
         <v>1</v>
       </c>
       <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5">
+        <v>84</v>
+      </c>
+      <c r="R5">
+        <v>25</v>
+      </c>
+      <c r="S5">
         <v>5</v>
       </c>
-      <c r="Q5">
+      <c r="T5">
         <v>6</v>
       </c>
-      <c r="R5">
+      <c r="U5">
         <v>9</v>
       </c>
-      <c r="S5" t="s">
-        <v>45</v>
+      <c r="V5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -799,13 +862,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -841,16 +904,25 @@
         <v>1</v>
       </c>
       <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6">
+        <v>74</v>
+      </c>
+      <c r="R6">
+        <v>20</v>
+      </c>
+      <c r="S6">
         <v>-15</v>
       </c>
-      <c r="Q6">
+      <c r="T6">
         <v>6</v>
       </c>
-      <c r="R6">
+      <c r="U6">
         <v>9</v>
       </c>
-      <c r="S6" t="s">
-        <v>49</v>
+      <c r="V6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -858,13 +930,13 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -900,16 +972,25 @@
         <v>1</v>
       </c>
       <c r="P7">
+        <v>30</v>
+      </c>
+      <c r="Q7">
+        <v>79</v>
+      </c>
+      <c r="R7">
+        <v>20</v>
+      </c>
+      <c r="S7">
         <v>-10</v>
       </c>
-      <c r="Q7">
+      <c r="T7">
         <v>6</v>
       </c>
-      <c r="R7">
+      <c r="U7">
         <v>9</v>
       </c>
-      <c r="S7" t="s">
-        <v>53</v>
+      <c r="V7" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -917,13 +998,13 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E8">
         <v>25</v>
@@ -959,16 +1040,25 @@
         <v>1</v>
       </c>
       <c r="P8">
+        <v>30</v>
+      </c>
+      <c r="Q8">
+        <v>89</v>
+      </c>
+      <c r="R8">
+        <v>30</v>
+      </c>
+      <c r="S8">
         <v>20</v>
       </c>
-      <c r="Q8">
+      <c r="T8">
         <v>6</v>
       </c>
-      <c r="R8">
+      <c r="U8">
         <v>9</v>
       </c>
-      <c r="S8" t="s">
-        <v>45</v>
+      <c r="V8" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -976,13 +1066,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E9">
         <v>30</v>
@@ -1018,16 +1108,25 @@
         <v>1</v>
       </c>
       <c r="P9">
+        <v>30</v>
+      </c>
+      <c r="Q9">
+        <v>92</v>
+      </c>
+      <c r="R9">
+        <v>25</v>
+      </c>
+      <c r="S9">
         <v>20</v>
       </c>
-      <c r="Q9">
+      <c r="T9">
         <v>6</v>
       </c>
-      <c r="R9">
+      <c r="U9">
         <v>9</v>
       </c>
-      <c r="S9" t="s">
-        <v>45</v>
+      <c r="V9" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
